--- a/programme/chair-sheets/S34.xlsx
+++ b/programme/chair-sheets/S34.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">ICCCMLA 2026 - Session attendance and evaluation sheet</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t xml:space="preserve">Hybrid Customer Analytics via Recency, Frequency, and Monetary (RFM) Clustering and Propensity Modeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved to Tue 6 Oct, Session 15, 11:12 IST - do not mark here</t>
   </si>
   <si>
     <t xml:space="preserve">13:37-13:49</t>
@@ -225,7 +231,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +291,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <strike val="true"/>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF555555"/>
@@ -293,7 +314,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,13 +330,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3EFF7"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFE3EFF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -368,7 +395,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -417,6 +444,26 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -425,7 +472,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -455,7 +502,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -473,7 +520,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -960,42 +1007,46 @@
       <c r="L15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="11" t="str">
+      <c r="E16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12" t="str">
         <f aca="false">IF(COUNT(G16:I16)=0,"",SUM(G16:I16))</f>
         <v/>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="16" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
@@ -1014,13 +1065,13 @@
         <v>8</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
@@ -1036,203 +1087,203 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="12" t="n">
-        <f aca="false">COUNTA(C11:C18)</f>
-        <v>8</v>
+      <c r="E20" s="17" t="n">
+        <f aca="false">COUNTA(C11:C18)-COUNTIF(E11:E18,"Moved")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">COUNTIF(E11:E18,"Present")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="17" t="n">
         <f aca="false">COUNTIF(E11:E18,"Late")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="17" t="n">
         <f aca="false">COUNTIF(E11:E18,"Absent")</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="17" t="n">
         <f aca="false">COUNTA(C11:C18)-COUNTA(E11:E18)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="17" t="n">
         <f aca="false">COUNTIF(K11:K18,"Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="A33" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="A34" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="A35" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
+      <c r="A36" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
+      <c r="A37" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
